--- a/data/sync_databases/BD_Tarimas.xlsx
+++ b/data/sync_databases/BD_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I473"/>
+  <dimension ref="A1:I474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21695,9 +21695,54 @@
         </is>
       </c>
       <c r="H473" t="b">
+        <v>0</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>TPM-0515</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H474" t="b">
         <v>1</v>
       </c>
-      <c r="I473" t="inlineStr">
+      <c r="I474" t="inlineStr">
         <is>
           <t>Planta 1 - Sigrama Diagonal</t>
         </is>

--- a/data/sync_databases/BD_Tarimas.xlsx
+++ b/data/sync_databases/BD_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I474"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H292" t="b">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H293" t="b">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H401" t="b">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H413" t="b">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H456" t="b">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H457" t="b">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H459" t="b">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H460" t="b">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>Disponible</t>
+          <t>Remesada</t>
         </is>
       </c>
       <c r="H461" t="b">
@@ -21736,13 +21736,1498 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H474" t="b">
+        <v>0</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>TPM-0516</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H475" t="b">
+        <v>0</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>TPM-0517</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H476" t="b">
+        <v>0</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>TPM-0518</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H477" t="b">
+        <v>0</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>TPM-0519</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H478" t="b">
+        <v>0</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>TPM-0520</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Bulto_3</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H479" t="b">
+        <v>0</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>TPM-0521</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Bulto_4</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H480" t="b">
+        <v>0</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>TPM-0522</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H481" t="b">
+        <v>0</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>TPM-0523</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H482" t="b">
+        <v>0</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>TPM-0524</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H483" t="b">
+        <v>0</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>TPM-0525</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H484" t="b">
+        <v>0</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>TPM-0526</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Bulto_3</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H485" t="b">
+        <v>0</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>TPM-0527</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
           <t>Disponible</t>
         </is>
       </c>
-      <c r="H474" t="b">
+      <c r="H486" t="b">
+        <v>0</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>TPM-0528</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H487" t="b">
+        <v>0</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>TPM-0529</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Bulto_3</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H488" t="b">
+        <v>0</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>TPM-0530</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Bulto_4</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H489" t="b">
+        <v>0</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>TPM-0531</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Bulto_5</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H490" t="b">
+        <v>0</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>TPM-0532</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Bulto_6</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H491" t="b">
+        <v>0</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>TPM-0533</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Bulto_7</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H492" t="b">
+        <v>0</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>TPM-0534</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Bulto_8</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H493" t="b">
+        <v>0</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>TPM-0535</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Bulto_9</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H494" t="b">
+        <v>0</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>TPM-0536</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Bulto_10</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H495" t="b">
+        <v>0</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>TPM-0537</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Bulto_11</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H496" t="b">
+        <v>0</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>TPM-0538</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Bulto_12</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H497" t="b">
+        <v>0</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>TPM-0539</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H498" t="b">
+        <v>0</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>TPM-0540</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H499" t="b">
+        <v>0</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>TPM-0541</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H500" t="b">
+        <v>0</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>TPM-0542</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H501" t="b">
+        <v>0</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>TPM-0543</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Bulto_2</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H502" t="b">
+        <v>0</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>TPM-0544</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Bulto_3</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H503" t="b">
+        <v>0</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>TPM-0545</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Bulto_4</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H504" t="b">
+        <v>0</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>TPM-0546</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Bulto_5</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H505" t="b">
+        <v>0</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>TPM-0547</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Bulto_6</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Remesada</t>
+        </is>
+      </c>
+      <c r="H506" t="b">
+        <v>0</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>TPM-0548</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Bulto_1</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Planta 1 - Sigrama Diagonal</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Luis Quintana</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Cuadrada</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="H507" t="b">
         <v>1</v>
       </c>
-      <c r="I474" t="inlineStr">
+      <c r="I507" t="inlineStr">
         <is>
           <t>Planta 1 - Sigrama Diagonal</t>
         </is>
